--- a/kompetenzliste.xlsx
+++ b/kompetenzliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Google Drive\mathechecks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fue\Meine Ablage\mathechecks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C36BD08-CFFF-4755-8574-67C2372A17AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735152A3-4ED4-41F0-B634-8C2CC0A4B86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="596">
   <si>
     <t>Lernbereich</t>
   </si>
@@ -1786,6 +1786,33 @@
   </si>
   <si>
     <t>LineareAlgebra_Wirtschaft_Mehrstufige Produktionsprozesse_Mengenvektoren_var2</t>
+  </si>
+  <si>
+    <t>produktlebenszyklus</t>
+  </si>
+  <si>
+    <t>Analysis_Wirtschaft_Produktlebenszyklus_KennzahlenGraphisch_Umsatz</t>
+  </si>
+  <si>
+    <t>Kenzahlen des Produktlebenszyklus berechnen (ohne Integration).</t>
+  </si>
+  <si>
+    <t>Analysis_Wirtschaft_Produktlebenszyklus_KennzahlenGraphisch_Abeitung</t>
+  </si>
+  <si>
+    <t>Analysis_Wirtschaft_Produktlebenszyklus_KennzahlenRechnerisch_gesamt</t>
+  </si>
+  <si>
+    <t>Kenzahlen des Produktlebenszyklus berechnen (mit Integration).</t>
+  </si>
+  <si>
+    <t>Kennzahlen des EKG-Zyklus berechnen</t>
+  </si>
+  <si>
+    <t>den Graphen der Produktlebenszyklusfunktion interpretieren.</t>
+  </si>
+  <si>
+    <t>den Graphen der Ableitung der Produktlebenszyklusfunktion interpretieren.</t>
   </si>
 </sst>
 </file>
@@ -1807,15 +1834,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1841,11 +1874,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1874,6 +1918,9 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1892,8 +1939,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle3" displayName="Tabelle3" ref="A1:H89" totalsRowShown="0">
-  <autoFilter ref="A1:H89" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle3" displayName="Tabelle3" ref="A1:H94" totalsRowShown="0">
+  <autoFilter ref="A1:H94" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Gebiet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lernbereich"/>
@@ -1911,9 +1958,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle13" displayName="Tabelle13" ref="B1:I189" totalsRowShown="0">
   <autoFilter ref="B1:I189" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Matrizenrechnung"/>
+        <filter val="Produktlebenszyklus"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2219,20 +2266,20 @@
   <sheetPr codeName="Tabelle1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H94"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="90.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="90.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -2258,7 +2305,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>488</v>
       </c>
@@ -2284,7 +2331,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>488</v>
       </c>
@@ -2310,7 +2357,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>488</v>
       </c>
@@ -2336,7 +2383,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>488</v>
       </c>
@@ -2362,7 +2409,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>488</v>
       </c>
@@ -2388,7 +2435,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>488</v>
       </c>
@@ -2414,7 +2461,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>488</v>
       </c>
@@ -2440,7 +2487,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>488</v>
       </c>
@@ -2466,7 +2513,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>488</v>
       </c>
@@ -2492,7 +2539,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>488</v>
       </c>
@@ -2518,7 +2565,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>488</v>
       </c>
@@ -2544,7 +2591,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>488</v>
       </c>
@@ -2570,7 +2617,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>488</v>
       </c>
@@ -2596,7 +2643,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>488</v>
       </c>
@@ -2622,7 +2669,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>488</v>
       </c>
@@ -2648,7 +2695,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>488</v>
       </c>
@@ -2674,7 +2721,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>488</v>
       </c>
@@ -2700,7 +2747,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>488</v>
       </c>
@@ -2726,7 +2773,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>488</v>
       </c>
@@ -2752,7 +2799,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>488</v>
       </c>
@@ -2778,7 +2825,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>488</v>
       </c>
@@ -2804,7 +2851,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>488</v>
       </c>
@@ -2830,7 +2877,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>488</v>
       </c>
@@ -2856,7 +2903,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>488</v>
       </c>
@@ -2882,7 +2929,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>488</v>
       </c>
@@ -2908,7 +2955,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>488</v>
       </c>
@@ -2934,7 +2981,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>488</v>
       </c>
@@ -2960,7 +3007,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>488</v>
       </c>
@@ -2986,7 +3033,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>488</v>
       </c>
@@ -3012,7 +3059,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>488</v>
       </c>
@@ -3038,7 +3085,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>488</v>
       </c>
@@ -3064,7 +3111,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>488</v>
       </c>
@@ -3090,7 +3137,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>488</v>
       </c>
@@ -3116,7 +3163,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>488</v>
       </c>
@@ -3142,7 +3189,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>488</v>
       </c>
@@ -3168,7 +3215,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>488</v>
       </c>
@@ -3194,7 +3241,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>488</v>
       </c>
@@ -3220,7 +3267,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>488</v>
       </c>
@@ -3246,7 +3293,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>488</v>
       </c>
@@ -3272,7 +3319,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>488</v>
       </c>
@@ -3298,7 +3345,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>488</v>
       </c>
@@ -3324,7 +3371,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>488</v>
       </c>
@@ -3350,7 +3397,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>488</v>
       </c>
@@ -3376,7 +3423,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>488</v>
       </c>
@@ -3402,7 +3449,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>488</v>
       </c>
@@ -3428,7 +3475,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>488</v>
       </c>
@@ -3454,7 +3501,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>488</v>
       </c>
@@ -3480,7 +3527,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>488</v>
       </c>
@@ -3506,7 +3553,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>488</v>
       </c>
@@ -3532,7 +3579,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>488</v>
       </c>
@@ -3558,7 +3605,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>488</v>
       </c>
@@ -3584,7 +3631,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>488</v>
       </c>
@@ -3610,7 +3657,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>488</v>
       </c>
@@ -3636,7 +3683,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>541</v>
       </c>
@@ -3662,7 +3709,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>541</v>
       </c>
@@ -3688,7 +3735,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>541</v>
       </c>
@@ -3714,7 +3761,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>541</v>
       </c>
@@ -3740,7 +3787,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>541</v>
       </c>
@@ -3766,7 +3813,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>541</v>
       </c>
@@ -3792,7 +3839,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>541</v>
       </c>
@@ -3818,7 +3865,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>541</v>
       </c>
@@ -3844,7 +3891,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>541</v>
       </c>
@@ -3870,7 +3917,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>541</v>
       </c>
@@ -3896,7 +3943,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>541</v>
       </c>
@@ -3922,7 +3969,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>541</v>
       </c>
@@ -3948,7 +3995,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>541</v>
       </c>
@@ -3974,7 +4021,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>541</v>
       </c>
@@ -4000,7 +4047,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>541</v>
       </c>
@@ -4026,7 +4073,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>541</v>
       </c>
@@ -4052,7 +4099,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>541</v>
       </c>
@@ -4078,7 +4125,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>541</v>
       </c>
@@ -4104,7 +4151,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>541</v>
       </c>
@@ -4130,7 +4177,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>541</v>
       </c>
@@ -4156,7 +4203,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>541</v>
       </c>
@@ -4182,7 +4229,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>541</v>
       </c>
@@ -4208,7 +4255,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>541</v>
       </c>
@@ -4234,7 +4281,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>541</v>
       </c>
@@ -4260,7 +4307,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>572</v>
       </c>
@@ -4286,7 +4333,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>572</v>
       </c>
@@ -4312,7 +4359,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>572</v>
       </c>
@@ -4338,7 +4385,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>572</v>
       </c>
@@ -4364,7 +4411,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>572</v>
       </c>
@@ -4390,7 +4437,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>572</v>
       </c>
@@ -4416,7 +4463,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>572</v>
       </c>
@@ -4442,7 +4489,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>572</v>
       </c>
@@ -4468,7 +4515,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>572</v>
       </c>
@@ -4494,7 +4541,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>572</v>
       </c>
@@ -4520,7 +4567,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>572</v>
       </c>
@@ -4543,6 +4590,136 @@
         <v>496</v>
       </c>
       <c r="H89" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>541</v>
+      </c>
+      <c r="B90" t="s">
+        <v>587</v>
+      </c>
+      <c r="C90" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" s="8">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G90" t="s">
+        <v>496</v>
+      </c>
+      <c r="H90" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>541</v>
+      </c>
+      <c r="B91" t="s">
+        <v>587</v>
+      </c>
+      <c r="C91" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="8">
+        <v>2</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="G91" t="s">
+        <v>496</v>
+      </c>
+      <c r="H91" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>541</v>
+      </c>
+      <c r="B92" t="s">
+        <v>587</v>
+      </c>
+      <c r="C92" t="s">
+        <v>94</v>
+      </c>
+      <c r="D92" s="8">
+        <v>3</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G92" t="s">
+        <v>496</v>
+      </c>
+      <c r="H92" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>541</v>
+      </c>
+      <c r="B93" t="s">
+        <v>587</v>
+      </c>
+      <c r="C93" t="s">
+        <v>94</v>
+      </c>
+      <c r="D93" s="8">
+        <v>4</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G93" t="s">
+        <v>496</v>
+      </c>
+      <c r="H93" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>541</v>
+      </c>
+      <c r="B94" t="s">
+        <v>587</v>
+      </c>
+      <c r="C94" t="s">
+        <v>94</v>
+      </c>
+      <c r="D94" s="8">
+        <v>5</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G94" t="s">
+        <v>496</v>
+      </c>
+      <c r="H94" t="s">
         <v>493</v>
       </c>
     </row>
@@ -4560,20 +4737,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I189"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.73046875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1328125" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="75.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="62.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="162.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="75.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="62.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="162.265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.59765625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -4602,7 +4779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
@@ -4628,7 +4805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4654,7 +4831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -4680,7 +4857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
@@ -4706,7 +4883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -4730,7 +4907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -4754,7 +4931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
@@ -4778,7 +4955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -4802,7 +4979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
@@ -4826,7 +5003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -4850,7 +5027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
@@ -4874,7 +5051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
@@ -4896,7 +5073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -4918,7 +5095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
@@ -4942,7 +5119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -4966,7 +5143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4988,7 +5165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -5010,7 +5187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
@@ -5034,7 +5211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -5058,7 +5235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
@@ -5082,7 +5259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -5108,7 +5285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
@@ -5134,7 +5311,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
@@ -5160,7 +5337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>12</v>
       </c>
@@ -5186,7 +5363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
@@ -5212,7 +5389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
@@ -5238,7 +5415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>12</v>
       </c>
@@ -5264,7 +5441,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>12</v>
       </c>
@@ -5290,7 +5467,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -5316,7 +5493,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
@@ -5340,7 +5517,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>12</v>
       </c>
@@ -5364,7 +5541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -5390,7 +5567,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
@@ -5416,7 +5593,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
@@ -5442,7 +5619,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>12</v>
       </c>
@@ -5468,7 +5645,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>12</v>
       </c>
@@ -5494,7 +5671,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -5520,7 +5697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>12</v>
       </c>
@@ -5546,7 +5723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>12</v>
       </c>
@@ -5572,7 +5749,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
@@ -5598,7 +5775,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
@@ -5624,7 +5801,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
@@ -5650,7 +5827,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
@@ -5676,7 +5853,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
         <v>12</v>
       </c>
@@ -5702,7 +5879,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
         <v>12</v>
       </c>
@@ -5728,7 +5905,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
         <v>12</v>
       </c>
@@ -5754,7 +5931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
         <v>12</v>
       </c>
@@ -5780,7 +5957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B49" s="3" t="s">
         <v>12</v>
       </c>
@@ -5806,7 +5983,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
         <v>12</v>
       </c>
@@ -5832,7 +6009,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
         <v>12</v>
       </c>
@@ -5858,7 +6035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B52" s="3" t="s">
         <v>12</v>
       </c>
@@ -5884,7 +6061,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>12</v>
       </c>
@@ -5910,7 +6087,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -5936,7 +6113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B55" s="3" t="s">
         <v>12</v>
       </c>
@@ -5962,7 +6139,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="3" t="s">
         <v>12</v>
       </c>
@@ -5988,7 +6165,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
@@ -6014,7 +6191,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
         <v>12</v>
       </c>
@@ -6037,7 +6214,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
         <v>12</v>
       </c>
@@ -6058,7 +6235,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>12</v>
       </c>
@@ -6079,7 +6256,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="3" t="s">
         <v>12</v>
       </c>
@@ -6097,7 +6274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="3" t="s">
         <v>12</v>
       </c>
@@ -6115,7 +6292,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="3" t="s">
         <v>188</v>
       </c>
@@ -6138,7 +6315,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="3" t="s">
         <v>188</v>
       </c>
@@ -6161,7 +6338,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="3" t="s">
         <v>188</v>
       </c>
@@ -6184,7 +6361,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="3" t="s">
         <v>188</v>
       </c>
@@ -6207,7 +6384,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="67" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
         <v>188</v>
       </c>
@@ -6230,7 +6407,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="3" t="s">
         <v>188</v>
       </c>
@@ -6253,7 +6430,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="69" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B69" s="3" t="s">
         <v>188</v>
       </c>
@@ -6276,7 +6453,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
         <v>188</v>
       </c>
@@ -6299,7 +6476,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B71" s="3" t="s">
         <v>188</v>
       </c>
@@ -6323,7 +6500,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B72" s="3" t="s">
         <v>188</v>
       </c>
@@ -6347,7 +6524,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="73" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B73" s="3" t="s">
         <v>188</v>
       </c>
@@ -6371,7 +6548,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
         <v>188</v>
       </c>
@@ -6395,7 +6572,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B75" s="3" t="s">
         <v>188</v>
       </c>
@@ -6419,7 +6596,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
         <v>188</v>
       </c>
@@ -6443,7 +6620,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B77" s="3" t="s">
         <v>188</v>
       </c>
@@ -6467,7 +6644,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B78" s="3" t="s">
         <v>188</v>
       </c>
@@ -6491,7 +6668,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B79" s="3" t="s">
         <v>188</v>
       </c>
@@ -6517,7 +6694,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B80" s="3" t="s">
         <v>188</v>
       </c>
@@ -6543,7 +6720,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B81" s="3" t="s">
         <v>188</v>
       </c>
@@ -6569,7 +6746,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B82" s="3" t="s">
         <v>188</v>
       </c>
@@ -6595,7 +6772,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="83" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B83" s="3" t="s">
         <v>188</v>
       </c>
@@ -6621,7 +6798,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B84" s="3" t="s">
         <v>188</v>
       </c>
@@ -6647,7 +6824,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B85" s="3" t="s">
         <v>188</v>
       </c>
@@ -6671,7 +6848,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B86" s="3" t="s">
         <v>188</v>
       </c>
@@ -6695,7 +6872,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B87" s="3" t="s">
         <v>188</v>
       </c>
@@ -6719,7 +6896,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B88" s="3" t="s">
         <v>188</v>
       </c>
@@ -6743,7 +6920,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B89" s="3" t="s">
         <v>188</v>
       </c>
@@ -6767,7 +6944,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B90" s="3" t="s">
         <v>242</v>
       </c>
@@ -6791,7 +6968,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="91" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B91" s="3" t="s">
         <v>242</v>
       </c>
@@ -6815,7 +6992,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="92" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B92" s="3" t="s">
         <v>242</v>
       </c>
@@ -6839,7 +7016,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="93" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B93" s="3" t="s">
         <v>242</v>
       </c>
@@ -6863,7 +7040,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="94" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B94" s="3" t="s">
         <v>242</v>
       </c>
@@ -6887,7 +7064,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B95" s="3" t="s">
         <v>242</v>
       </c>
@@ -6911,7 +7088,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B96" s="3" t="s">
         <v>242</v>
       </c>
@@ -6935,7 +7112,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B97" s="3" t="s">
         <v>242</v>
       </c>
@@ -6959,7 +7136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B98" s="3" t="s">
         <v>242</v>
       </c>
@@ -6983,7 +7160,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B99" s="3" t="s">
         <v>242</v>
       </c>
@@ -7007,7 +7184,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B100" s="3" t="s">
         <v>242</v>
       </c>
@@ -7031,7 +7208,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B101" s="3" t="s">
         <v>242</v>
       </c>
@@ -7055,7 +7232,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B102" s="3" t="s">
         <v>242</v>
       </c>
@@ -7079,7 +7256,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B103" s="3" t="s">
         <v>242</v>
       </c>
@@ -7103,7 +7280,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B104" s="3" t="s">
         <v>242</v>
       </c>
@@ -7127,7 +7304,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B105" s="3" t="s">
         <v>242</v>
       </c>
@@ -7151,7 +7328,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="106" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B106" s="3" t="s">
         <v>242</v>
       </c>
@@ -7175,7 +7352,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="107" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B107" s="3" t="s">
         <v>242</v>
       </c>
@@ -7199,7 +7376,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="2:9" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B108" s="3" t="s">
         <v>242</v>
       </c>
@@ -7225,7 +7402,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="109" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B109" s="3" t="s">
         <v>289</v>
       </c>
@@ -7246,7 +7423,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="110" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B110" s="3" t="s">
         <v>289</v>
       </c>
@@ -7267,7 +7444,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="111" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B111" s="3" t="s">
         <v>289</v>
       </c>
@@ -7288,7 +7465,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="112" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B112" s="3" t="s">
         <v>289</v>
       </c>
@@ -7309,7 +7486,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="113" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B113" s="3" t="s">
         <v>289</v>
       </c>
@@ -7330,7 +7507,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="114" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B114" s="3" t="s">
         <v>289</v>
       </c>
@@ -7351,7 +7528,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B115" s="3" t="s">
         <v>289</v>
       </c>
@@ -7372,7 +7549,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B116" s="3" t="s">
         <v>289</v>
       </c>
@@ -7393,7 +7570,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B117" s="3" t="s">
         <v>289</v>
       </c>
@@ -7414,7 +7591,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B118" s="3" t="s">
         <v>289</v>
       </c>
@@ -7435,7 +7612,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="119" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B119" s="3" t="s">
         <v>289</v>
       </c>
@@ -7456,7 +7633,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="120" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B120" s="3" t="s">
         <v>289</v>
       </c>
@@ -7477,7 +7654,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="121" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B121" s="3" t="s">
         <v>289</v>
       </c>
@@ -7498,7 +7675,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="122" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B122" s="3" t="s">
         <v>289</v>
       </c>
@@ -7519,7 +7696,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B123" s="3" t="s">
         <v>289</v>
       </c>
@@ -7540,7 +7717,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="124" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B124" s="3" t="s">
         <v>289</v>
       </c>
@@ -7561,7 +7738,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="125" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B125" s="3" t="s">
         <v>289</v>
       </c>
@@ -7582,7 +7759,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="126" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B126" s="3" t="s">
         <v>289</v>
       </c>
@@ -7603,7 +7780,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="127" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B127" s="3" t="s">
         <v>289</v>
       </c>
@@ -7626,7 +7803,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="128" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B128" s="3" t="s">
         <v>289</v>
       </c>
@@ -7649,7 +7826,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="129" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B129" s="3" t="s">
         <v>289</v>
       </c>
@@ -7672,7 +7849,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="130" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B130" s="3" t="s">
         <v>289</v>
       </c>
@@ -7695,7 +7872,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="131" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B131" s="3" t="s">
         <v>289</v>
       </c>
@@ -7718,7 +7895,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="132" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B132" s="3" t="s">
         <v>289</v>
       </c>
@@ -7741,7 +7918,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="133" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B133" s="3" t="s">
         <v>289</v>
       </c>
@@ -7764,7 +7941,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="134" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B134" s="3" t="s">
         <v>289</v>
       </c>
@@ -7787,7 +7964,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="135" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B135" s="3" t="s">
         <v>289</v>
       </c>
@@ -7810,7 +7987,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="136" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B136" s="3" t="s">
         <v>22</v>
       </c>
@@ -7834,7 +8011,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="137" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B137" s="3" t="s">
         <v>22</v>
       </c>
@@ -7858,7 +8035,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="138" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B138" s="3" t="s">
         <v>22</v>
       </c>
@@ -7882,7 +8059,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="139" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B139" s="3" t="s">
         <v>22</v>
       </c>
@@ -7906,7 +8083,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="140" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B140" s="3" t="s">
         <v>22</v>
       </c>
@@ -7930,7 +8107,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="141" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B141" s="3" t="s">
         <v>22</v>
       </c>
@@ -7954,7 +8131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="142" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B142" s="3" t="s">
         <v>22</v>
       </c>
@@ -7978,7 +8155,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="143" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B143" s="3" t="s">
         <v>22</v>
       </c>
@@ -8004,7 +8181,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="144" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B144" s="3" t="s">
         <v>22</v>
       </c>
@@ -8028,7 +8205,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="145" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B145" s="3" t="s">
         <v>22</v>
       </c>
@@ -8052,7 +8229,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="146" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B146" s="3" t="s">
         <v>22</v>
       </c>
@@ -8078,7 +8255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B147" s="3" t="s">
         <v>22</v>
       </c>
@@ -8104,7 +8281,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="148" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B148" s="3" t="s">
         <v>22</v>
       </c>
@@ -8130,7 +8307,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="149" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B149" s="3" t="s">
         <v>22</v>
       </c>
@@ -8154,7 +8331,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="150" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B150" s="3" t="s">
         <v>22</v>
       </c>
@@ -8180,7 +8357,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B151" s="3" t="s">
         <v>22</v>
       </c>
@@ -8206,7 +8383,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="152" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B152" s="3" t="s">
         <v>22</v>
       </c>
@@ -8232,7 +8409,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="153" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B153" s="3" t="s">
         <v>22</v>
       </c>
@@ -8258,7 +8435,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="154" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B154" s="3" t="s">
         <v>22</v>
       </c>
@@ -8284,7 +8461,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="155" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B155" s="3" t="s">
         <v>22</v>
       </c>
@@ -8308,7 +8485,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B156" s="3" t="s">
         <v>22</v>
       </c>
@@ -8332,7 +8509,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="157" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B157" s="3" t="s">
         <v>22</v>
       </c>
@@ -8356,7 +8533,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="158" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B158" s="3" t="s">
         <v>22</v>
       </c>
@@ -8378,7 +8555,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="159" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B159" s="3" t="s">
         <v>22</v>
       </c>
@@ -8397,7 +8574,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="160" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B160" s="3" t="s">
         <v>22</v>
       </c>
@@ -8416,7 +8593,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="161" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B161" s="3" t="s">
         <v>22</v>
       </c>
@@ -8437,7 +8614,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="162" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B162" s="3" t="s">
         <v>22</v>
       </c>
@@ -8463,7 +8640,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="163" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B163" s="3" t="s">
         <v>22</v>
       </c>
@@ -8489,7 +8666,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="164" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B164" s="3" t="s">
         <v>22</v>
       </c>
@@ -8515,7 +8692,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="165" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B165" s="3" t="s">
         <v>22</v>
       </c>
@@ -8541,7 +8718,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="166" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B166" s="3" t="s">
         <v>22</v>
       </c>
@@ -8567,7 +8744,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="167" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B167" s="3" t="s">
         <v>22</v>
       </c>
@@ -8593,7 +8770,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="168" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B168" s="3" t="s">
         <v>22</v>
       </c>
@@ -8617,7 +8794,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="169" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B169" s="3" t="s">
         <v>22</v>
       </c>
@@ -8641,7 +8818,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="170" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B170" s="3" t="s">
         <v>22</v>
       </c>
@@ -8665,7 +8842,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="171" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B171" s="3" t="s">
         <v>22</v>
       </c>
@@ -8689,7 +8866,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="172" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B172" s="3" t="s">
         <v>22</v>
       </c>
@@ -8713,7 +8890,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="173" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B173" s="3" t="s">
         <v>22</v>
       </c>
@@ -8737,7 +8914,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="174" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B174" s="3" t="s">
         <v>22</v>
       </c>
@@ -8761,7 +8938,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="175" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B175" s="3" t="s">
         <v>22</v>
       </c>
@@ -8785,7 +8962,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="176" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B176" s="3" t="s">
         <v>22</v>
       </c>
@@ -8809,7 +8986,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="177" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B177" s="3" t="s">
         <v>22</v>
       </c>
@@ -8833,7 +9010,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="178" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B178" s="3" t="s">
         <v>22</v>
       </c>
@@ -8857,7 +9034,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="179" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B179" s="3" t="s">
         <v>22</v>
       </c>
@@ -8881,7 +9058,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="180" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B180" s="3" t="s">
         <v>22</v>
       </c>
@@ -8905,7 +9082,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="181" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B181" s="3" t="s">
         <v>22</v>
       </c>
@@ -8929,7 +9106,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="182" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B182" s="3" t="s">
         <v>22</v>
       </c>
@@ -8953,7 +9130,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="183" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B183" s="3" t="s">
         <v>22</v>
       </c>
@@ -8977,7 +9154,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="184" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B184" s="3" t="s">
         <v>22</v>
       </c>
@@ -9001,7 +9178,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="185" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B185" s="3" t="s">
         <v>22</v>
       </c>
@@ -9025,7 +9202,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="186" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B186" s="3" t="s">
         <v>22</v>
       </c>
@@ -9049,7 +9226,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="187" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B187" s="3" t="s">
         <v>22</v>
       </c>
@@ -9073,7 +9250,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="188" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B188" s="3" t="s">
         <v>22</v>
       </c>
@@ -9097,7 +9274,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="189" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" s="5" customFormat="1" ht="32.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B189" s="3" t="s">
         <v>22</v>
       </c>
@@ -9135,14 +9312,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9153,7 +9330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -9161,7 +9338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -9169,7 +9346,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -9177,7 +9354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -9185,7 +9362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9193,7 +9370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -9201,7 +9378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -9209,7 +9386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -9217,7 +9394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -9225,7 +9402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -9233,7 +9410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
